--- a/deliverables/uiss/X5_UISS_Batch_ActualDemandSummarySync.xlsx
+++ b/deliverables/uiss/X5_UISS_Batch_ActualDemandSummarySync.xlsx
@@ -5067,13 +5067,13 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>57150</xdr:colOff>
       <xdr:row>28</xdr:row>
       <xdr:rowOff>35549</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>44409</xdr:colOff>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>82509</xdr:colOff>
       <xdr:row>31</xdr:row>
       <xdr:rowOff>69839</xdr:rowOff>
     </xdr:to>
@@ -5084,8 +5084,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1190625" y="3942704"/>
-          <a:ext cx="1663659" cy="457200"/>
+          <a:off x="1247775" y="3942704"/>
+          <a:ext cx="1549359" cy="457200"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
           <a:avLst/>
@@ -5112,7 +5112,7 @@
               <a:latin typeface="Arial"/>
               <a:cs typeface="Arial"/>
             </a:rPr>
-            <a:t>Delete NSP table + insert</a:t>
+            <a:t>Delete Supplier System</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -5125,7 +5125,7 @@
               <a:latin typeface="Arial"/>
               <a:cs typeface="Arial"/>
             </a:rPr>
-            <a:t>all rows</a:t>
+            <a:t>table + insert all rows</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -5407,13 +5407,13 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>41</xdr:col>
-      <xdr:colOff>24939</xdr:colOff>
+      <xdr:colOff>47877</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>57424</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>41</xdr:col>
-      <xdr:colOff>34464</xdr:colOff>
+      <xdr:colOff>57402</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>31316</xdr:rowOff>
     </xdr:to>
@@ -5427,7 +5427,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="3882564" y="1598569"/>
+          <a:off x="3905502" y="1598569"/>
           <a:ext cx="1" cy="396802"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
@@ -5452,7 +5452,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>33</xdr:col>
-      <xdr:colOff>70690</xdr:colOff>
+      <xdr:colOff>93628</xdr:colOff>
       <xdr:row>15</xdr:row>
       <xdr:rowOff>109327</xdr:rowOff>
     </xdr:to>
@@ -5467,7 +5467,7 @@
       <xdr:spPr>
         <a:xfrm flipV="1">
           <a:off x="2593266" y="2201652"/>
-          <a:ext cx="573048" cy="1"/>
+          <a:ext cx="595987" cy="1"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -5486,7 +5486,7 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>41</xdr:col>
-      <xdr:colOff>24939</xdr:colOff>
+      <xdr:colOff>47877</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>20968</xdr:rowOff>
     </xdr:from>
@@ -5506,8 +5506,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3882564" y="2407933"/>
-          <a:ext cx="34407" cy="396884"/>
+          <a:off x="3905502" y="2407933"/>
+          <a:ext cx="11469" cy="396884"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -5906,14 +5906,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>90050</xdr:colOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>17738</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>67772</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>47</xdr:col>
-      <xdr:colOff>55078</xdr:colOff>
+      <xdr:colOff>78017</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>57424</xdr:rowOff>
     </xdr:to>
@@ -5924,7 +5924,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3280925" y="1186007"/>
+          <a:off x="3303863" y="1186007"/>
           <a:ext cx="1203278" cy="412562"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
@@ -5962,13 +5962,13 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>33</xdr:col>
-      <xdr:colOff>70690</xdr:colOff>
+      <xdr:colOff>93628</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>31316</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>48</xdr:col>
-      <xdr:colOff>74438</xdr:colOff>
+      <xdr:col>49</xdr:col>
+      <xdr:colOff>2126</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>20968</xdr:rowOff>
     </xdr:to>
@@ -5979,7 +5979,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3166315" y="1995371"/>
+          <a:off x="3189253" y="1995371"/>
           <a:ext cx="1432498" cy="412562"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
@@ -6016,14 +6016,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>59262</xdr:colOff>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>67153</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>135913</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>49</xdr:col>
-      <xdr:colOff>59431</xdr:colOff>
+      <xdr:col>48</xdr:col>
+      <xdr:colOff>51541</xdr:colOff>
       <xdr:row>22</xdr:row>
       <xdr:rowOff>125565</xdr:rowOff>
     </xdr:to>
@@ -6034,8 +6034,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3154887" y="2804818"/>
-          <a:ext cx="1524169" cy="412562"/>
+          <a:off x="3258028" y="2804818"/>
+          <a:ext cx="1317888" cy="412562"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
           <a:avLst/>
@@ -6062,7 +6062,7 @@
               <a:latin typeface="Arial"/>
               <a:cs typeface="Arial"/>
             </a:rPr>
-            <a:t>(3) Delete all rows of NSP</a:t>
+            <a:t>(3) Delete all rows of</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -6075,7 +6075,7 @@
               <a:latin typeface="Arial"/>
               <a:cs typeface="Arial"/>
             </a:rPr>
-            <a:t>table</a:t>
+            <a:t>Supplier System table</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -6418,7 +6418,7 @@
               <a:latin typeface="Arial"/>
               <a:cs typeface="Arial"/>
             </a:rPr>
-            <a:t>(NSP)</a:t>
+            <a:t>(Supplier System)</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -6905,7 +6905,7 @@
       <c r="BB2" s="721" t="n"/>
       <c r="BC2" s="931" t="inlineStr">
         <is>
-          <t>X5 Crossdock - Actual Demand Summary Sync to NSP</t>
+          <t>X5 Crossdock - Actual Demand Summary Sync to Supplier System</t>
         </is>
       </c>
       <c r="BD2" s="715" t="n"/>
@@ -12806,7 +12806,7 @@
       <c r="D10" s="941" t="n"/>
       <c r="E10" s="948" t="inlineStr">
         <is>
-          <t>the same name in NSP, so the DAD Volume Calculation and the Mapping Destination</t>
+          <t>the same name in Supplier System, so the DAD Volume Calculation and the Mapping</t>
         </is>
       </c>
       <c r="F10" s="941" t="n"/>
@@ -12931,7 +12931,7 @@
       <c r="D11" s="941" t="n"/>
       <c r="E11" s="948" t="inlineStr">
         <is>
-          <t>Calculation read the actual demand inside NSP.</t>
+          <t>Destination Calculation read the actual demand inside Supplier System.</t>
         </is>
       </c>
       <c r="F11" s="941" t="n"/>
@@ -13054,7 +13054,7 @@
       <c r="D12" s="941" t="n"/>
       <c r="E12" s="948" t="inlineStr">
         <is>
-          <t>The NSP table is fully replaced every run (delete - insert). In case any error occurs, the run is</t>
+          <t>The Supplier System table is fully replaced every run (delete - insert). In case any error</t>
         </is>
       </c>
       <c r="F12" s="941" t="n"/>
@@ -13167,7 +13167,7 @@
       <c r="D13" s="941" t="n"/>
       <c r="E13" s="948" t="inlineStr">
         <is>
-          <t>rolled back and NSP keeps the data of the last successful run.</t>
+          <t>occurs, the run is rolled back and Supplier System keeps the data of the last successful run.</t>
         </is>
       </c>
       <c r="F13" s="941" t="n"/>
@@ -13911,7 +13911,7 @@
       <c r="BD19" s="959" t="n"/>
       <c r="BE19" s="960" t="inlineStr">
         <is>
-          <t>(NSP)</t>
+          <t>(Supplier System)</t>
         </is>
       </c>
       <c r="BF19" s="961" t="n"/>
@@ -18986,7 +18986,7 @@
       <c r="CF18" s="999" t="n"/>
       <c r="CG18" s="1001" t="inlineStr">
         <is>
-          <t>SUMMARY (NSP).</t>
+          <t>SUMMARY (Supplier System).</t>
         </is>
       </c>
       <c r="CH18" s="999" t="n"/>
@@ -20407,7 +20407,7 @@
       <c r="CF31" s="999" t="n"/>
       <c r="CG31" s="1001" t="inlineStr">
         <is>
-          <t>leaves the NSP table empty or</t>
+          <t>leaves the Supplier System table</t>
         </is>
       </c>
       <c r="CH31" s="999" t="n"/>
@@ -20516,7 +20516,7 @@
       <c r="CF32" s="999" t="n"/>
       <c r="CG32" s="1001" t="inlineStr">
         <is>
-          <t>half filled.</t>
+          <t>empty or half filled.</t>
         </is>
       </c>
       <c r="CH32" s="999" t="n"/>
@@ -23123,7 +23123,7 @@
       <c r="J8" s="821" t="n"/>
       <c r="K8" s="1013" t="inlineStr">
         <is>
-          <t>TB_R_ACTUAL_DEMAND_SUMMARY (NSP)</t>
+          <t>TB_R_ACTUAL_DEMAND_SUMMARY (Supplier System)</t>
         </is>
       </c>
       <c r="L8" s="823" t="n"/>
@@ -23170,7 +23170,7 @@
       <c r="AW8" s="828" t="n"/>
       <c r="AX8" s="1014" t="inlineStr">
         <is>
-          <t>TB_R_ACTUAL_DEMAND_SUMMARY (NSP)</t>
+          <t>TB_R_ACTUAL_DEMAND_SUMMARY (Supplier System)</t>
         </is>
       </c>
       <c r="AY8" s="823" t="n"/>
@@ -27689,7 +27689,7 @@
       <c r="AW49" s="828" t="n"/>
       <c r="AX49" s="1014" t="inlineStr">
         <is>
-          <t>TB_R_ACTUAL_DEMAND_SUMMARY (NSP)</t>
+          <t>TB_R_ACTUAL_DEMAND_SUMMARY (Supplier System)</t>
         </is>
       </c>
       <c r="AY49" s="823" t="n"/>
@@ -33614,7 +33614,7 @@
       <c r="B8" s="942" t="n"/>
       <c r="C8" s="948" t="inlineStr">
         <is>
-          <t>This batch copies the actual demand summary from DB Surrounding into NSP once a month.</t>
+          <t>This batch copies the actual demand summary from DB Surrounding into Supplier System once a</t>
         </is>
       </c>
       <c r="D8" s="941" t="n"/>
@@ -33727,7 +33727,7 @@
       <c r="B9" s="942" t="n"/>
       <c r="C9" s="948" t="inlineStr">
         <is>
-          <t>Range of months and schedule are set in the system master (not explained in this document).</t>
+          <t>month. Range of months and schedule are set in the system master (not explained in this</t>
         </is>
       </c>
       <c r="D9" s="941" t="n"/>
@@ -33844,14 +33844,10 @@
       <c r="B10" s="942" t="n"/>
       <c r="C10" s="948" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" s="948" t="inlineStr">
-        <is>
-          <t>Full replace: all rows of the NSP table are deleted and all source rows are inserted (delete -</t>
-        </is>
-      </c>
+          <t>document).</t>
+        </is>
+      </c>
+      <c r="D10" s="941" t="n"/>
       <c r="E10" s="941" t="n"/>
       <c r="F10" s="941" t="n"/>
       <c r="G10" s="941" t="n"/>
@@ -33963,10 +33959,14 @@
     <row r="11" ht="11.1" customHeight="1" s="710">
       <c r="A11" s="941" t="n"/>
       <c r="B11" s="942" t="n"/>
-      <c r="C11" s="941" t="n"/>
+      <c r="C11" s="948" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D11" s="948" t="inlineStr">
         <is>
-          <t>insert). No row is compared or merged.</t>
+          <t>Full replace: all rows of the Supplier System table are deleted and all source rows are inserted</t>
         </is>
       </c>
       <c r="E11" s="941" t="n"/>
@@ -34080,14 +34080,10 @@
     <row r="12" ht="11.1" customHeight="1" s="710">
       <c r="A12" s="941" t="n"/>
       <c r="B12" s="942" t="n"/>
-      <c r="C12" s="948" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C12" s="941" t="n"/>
       <c r="D12" s="948" t="inlineStr">
         <is>
-          <t>All columns are copied with the same names and values; no conversion is done.</t>
+          <t>(delete - insert). No row is compared or merged.</t>
         </is>
       </c>
       <c r="E12" s="941" t="n"/>
@@ -34208,7 +34204,7 @@
       </c>
       <c r="D13" s="948" t="inlineStr">
         <is>
-          <t>Delete and insert run in one transaction (all-or-nothing). When the run fails, NSP keeps the data</t>
+          <t>All columns are copied with the same names and values; no conversion is done.</t>
         </is>
       </c>
       <c r="E13" s="941" t="n"/>
@@ -34322,10 +34318,14 @@
     <row r="14" ht="11.1" customHeight="1" s="710">
       <c r="A14" s="941" t="n"/>
       <c r="B14" s="942" t="n"/>
-      <c r="C14" s="941" t="n"/>
+      <c r="C14" s="948" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D14" s="948" t="inlineStr">
         <is>
-          <t>of the last successful run.</t>
+          <t>Delete and insert run in one transaction (all-or-nothing). When the run fails, Supplier System</t>
         </is>
       </c>
       <c r="E14" s="941" t="n"/>
@@ -34439,14 +34439,10 @@
     <row r="15" ht="11.1" customHeight="1" s="710">
       <c r="A15" s="941" t="n"/>
       <c r="B15" s="942" t="n"/>
-      <c r="C15" s="948" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C15" s="941" t="n"/>
       <c r="D15" s="948" t="inlineStr">
         <is>
-          <t>The batch must finish before the DAD Volume Calculation starts.</t>
+          <t>keeps the data of the last successful run.</t>
         </is>
       </c>
       <c r="E15" s="941" t="n"/>
@@ -34560,8 +34556,16 @@
     <row r="16" ht="11.1" customHeight="1" s="710">
       <c r="A16" s="941" t="n"/>
       <c r="B16" s="942" t="n"/>
-      <c r="C16" s="941" t="n"/>
-      <c r="D16" s="941" t="n"/>
+      <c r="C16" s="948" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D16" s="948" t="inlineStr">
+        <is>
+          <t>The batch must finish before the DAD Volume Calculation starts.</t>
+        </is>
+      </c>
       <c r="E16" s="941" t="n"/>
       <c r="F16" s="941" t="n"/>
       <c r="G16" s="941" t="n"/>
@@ -39639,7 +39643,7 @@
       <c r="S16" s="955" t="n"/>
       <c r="T16" s="1031" t="inlineStr">
         <is>
-          <t>Insert into the NSP table fails</t>
+          <t>Insert into the Supplier System</t>
         </is>
       </c>
       <c r="U16" s="957" t="n"/>
@@ -39760,7 +39764,11 @@
       <c r="Q17" s="961" t="n"/>
       <c r="R17" s="961" t="n"/>
       <c r="S17" s="959" t="n"/>
-      <c r="T17" s="1038" t="n"/>
+      <c r="T17" s="1039" t="inlineStr">
+        <is>
+          <t>table fails</t>
+        </is>
+      </c>
       <c r="U17" s="961" t="n"/>
       <c r="V17" s="961" t="n"/>
       <c r="W17" s="961" t="n"/>
@@ -39792,7 +39800,7 @@
       <c r="AW17" s="959" t="n"/>
       <c r="AX17" s="1041" t="inlineStr">
         <is>
-          <t>TB_R_ACTUAL_DEMAND_SUMMARY into NSP:</t>
+          <t>TB_R_ACTUAL_DEMAND_SUMMARY into</t>
         </is>
       </c>
       <c r="AY17" s="961" t="n"/>
@@ -39903,7 +39911,7 @@
       <c r="AW18" s="965" t="n"/>
       <c r="AX18" s="1036" t="inlineStr">
         <is>
-          <t>&lt;ERROR_DETAIL&gt;.</t>
+          <t>Supplier System: &lt;ERROR_DETAIL&gt;.</t>
         </is>
       </c>
       <c r="AY18" s="967" t="n"/>
@@ -44239,7 +44247,7 @@
       <c r="D13" s="941" t="n"/>
       <c r="E13" s="948" t="inlineStr">
         <is>
-          <t>Transaction table - Actual demand summary replicated from DB Surrounding to NSP (same columns). Key (PK) proposed from the data; types follow the source table.</t>
+          <t>Transaction table - Actual demand summary replicated from DB Surrounding to Supplier System (same columns). Key (PK) proposed from the data; types follow the source table.</t>
         </is>
       </c>
       <c r="F13" s="941" t="n"/>
@@ -48534,7 +48542,7 @@
     <row r="1">
       <c r="A1" s="1044" t="inlineStr">
         <is>
-          <t>Sample data - Actual Demand Summary Sync to NSP</t>
+          <t>Sample data - Actual Demand Summary Sync to Supplier System</t>
         </is>
       </c>
     </row>
@@ -48548,7 +48556,7 @@
     <row r="3">
       <c r="A3" s="1045" t="inlineStr">
         <is>
-          <t>The batch copies every row of the source table; the NSP table is emptied first (delete - insert).</t>
+          <t>The batch copies every row of the source table; the Supplier System table is emptied first (delete - insert).</t>
         </is>
       </c>
     </row>
@@ -48843,7 +48851,7 @@
       </c>
       <c r="C16" s="1048" t="inlineStr">
         <is>
-          <t>NSP table emptied, 349,225 rows inserted. Log STATUS = SUCCESS.</t>
+          <t>Supplier System table emptied, 349,225 rows inserted. Log STATUS = SUCCESS.</t>
         </is>
       </c>
     </row>
@@ -48860,7 +48868,7 @@
       </c>
       <c r="C17" s="1048" t="inlineStr">
         <is>
-          <t>The row no longer exists in NSP (full replace).</t>
+          <t>The row no longer exists in Supplier System (full replace).</t>
         </is>
       </c>
     </row>
@@ -48877,7 +48885,7 @@
       </c>
       <c r="C18" s="1048" t="inlineStr">
         <is>
-          <t>Rolled back: NSP keeps the data of the last successful run. Log STATUS = FAILED.</t>
+          <t>Rolled back: Supplier System keeps the data of the last successful run. Log STATUS = FAILED.</t>
         </is>
       </c>
     </row>

--- a/deliverables/uiss/X5_UISS_Batch_ActualDemandSummarySync.xlsx
+++ b/deliverables/uiss/X5_UISS_Batch_ActualDemandSummarySync.xlsx
@@ -5067,13 +5067,13 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>28</xdr:row>
       <xdr:rowOff>35549</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>82509</xdr:colOff>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>44409</xdr:colOff>
       <xdr:row>31</xdr:row>
       <xdr:rowOff>69839</xdr:rowOff>
     </xdr:to>
@@ -5084,8 +5084,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1247775" y="3942704"/>
-          <a:ext cx="1549359" cy="457200"/>
+          <a:off x="1190625" y="3942704"/>
+          <a:ext cx="1663659" cy="457200"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
           <a:avLst/>
@@ -5112,7 +5112,7 @@
               <a:latin typeface="Arial"/>
               <a:cs typeface="Arial"/>
             </a:rPr>
-            <a:t>Delete Supplier System</a:t>
+            <a:t>Delete NSP table + insert</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -5125,7 +5125,7 @@
               <a:latin typeface="Arial"/>
               <a:cs typeface="Arial"/>
             </a:rPr>
-            <a:t>table + insert all rows</a:t>
+            <a:t>all rows</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -5407,13 +5407,13 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>41</xdr:col>
-      <xdr:colOff>47877</xdr:colOff>
+      <xdr:colOff>24939</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>57424</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>41</xdr:col>
-      <xdr:colOff>57402</xdr:colOff>
+      <xdr:colOff>34464</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>31316</xdr:rowOff>
     </xdr:to>
@@ -5427,7 +5427,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="3905502" y="1598569"/>
+          <a:off x="3882564" y="1598569"/>
           <a:ext cx="1" cy="396802"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
@@ -5452,7 +5452,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>33</xdr:col>
-      <xdr:colOff>93628</xdr:colOff>
+      <xdr:colOff>70690</xdr:colOff>
       <xdr:row>15</xdr:row>
       <xdr:rowOff>109327</xdr:rowOff>
     </xdr:to>
@@ -5467,7 +5467,7 @@
       <xdr:spPr>
         <a:xfrm flipV="1">
           <a:off x="2593266" y="2201652"/>
-          <a:ext cx="595987" cy="1"/>
+          <a:ext cx="573048" cy="1"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -5486,7 +5486,7 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>41</xdr:col>
-      <xdr:colOff>47877</xdr:colOff>
+      <xdr:colOff>24939</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>20968</xdr:rowOff>
     </xdr:from>
@@ -5506,8 +5506,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3905502" y="2407933"/>
-          <a:ext cx="11469" cy="396884"/>
+          <a:off x="3882564" y="2407933"/>
+          <a:ext cx="34407" cy="396884"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -5906,14 +5906,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>17738</xdr:colOff>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>90050</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>67772</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>47</xdr:col>
-      <xdr:colOff>78017</xdr:colOff>
+      <xdr:colOff>55078</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>57424</xdr:rowOff>
     </xdr:to>
@@ -5924,7 +5924,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3303863" y="1186007"/>
+          <a:off x="3280925" y="1186007"/>
           <a:ext cx="1203278" cy="412562"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
@@ -5962,13 +5962,13 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>33</xdr:col>
-      <xdr:colOff>93628</xdr:colOff>
+      <xdr:colOff>70690</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>31316</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>49</xdr:col>
-      <xdr:colOff>2126</xdr:colOff>
+      <xdr:col>48</xdr:col>
+      <xdr:colOff>74438</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>20968</xdr:rowOff>
     </xdr:to>
@@ -5979,7 +5979,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3189253" y="1995371"/>
+          <a:off x="3166315" y="1995371"/>
           <a:ext cx="1432498" cy="412562"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
@@ -6016,14 +6016,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>67153</xdr:colOff>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>59262</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>135913</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>48</xdr:col>
-      <xdr:colOff>51541</xdr:colOff>
+      <xdr:col>49</xdr:col>
+      <xdr:colOff>59431</xdr:colOff>
       <xdr:row>22</xdr:row>
       <xdr:rowOff>125565</xdr:rowOff>
     </xdr:to>
@@ -6034,8 +6034,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3258028" y="2804818"/>
-          <a:ext cx="1317888" cy="412562"/>
+          <a:off x="3154887" y="2804818"/>
+          <a:ext cx="1524169" cy="412562"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartProcess">
           <a:avLst/>
@@ -6062,7 +6062,7 @@
               <a:latin typeface="Arial"/>
               <a:cs typeface="Arial"/>
             </a:rPr>
-            <a:t>(3) Delete all rows of</a:t>
+            <a:t>(3) Delete all rows of NSP</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -6075,7 +6075,7 @@
               <a:latin typeface="Arial"/>
               <a:cs typeface="Arial"/>
             </a:rPr>
-            <a:t>Supplier System table</a:t>
+            <a:t>table</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -6418,7 +6418,7 @@
               <a:latin typeface="Arial"/>
               <a:cs typeface="Arial"/>
             </a:rPr>
-            <a:t>(Supplier System)</a:t>
+            <a:t>(NSP)</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -6905,7 +6905,7 @@
       <c r="BB2" s="721" t="n"/>
       <c r="BC2" s="931" t="inlineStr">
         <is>
-          <t>X5 Crossdock - Actual Demand Summary Sync to Supplier System</t>
+          <t>X5 Crossdock - Actual Demand Summary Sync to NSP</t>
         </is>
       </c>
       <c r="BD2" s="715" t="n"/>
@@ -12806,7 +12806,7 @@
       <c r="D10" s="941" t="n"/>
       <c r="E10" s="948" t="inlineStr">
         <is>
-          <t>the same name in Supplier System, so the DAD Volume Calculation and the Mapping</t>
+          <t>the same name in NSP, so the DAD Volume Calculation and the Mapping Destination</t>
         </is>
       </c>
       <c r="F10" s="941" t="n"/>
@@ -12931,7 +12931,7 @@
       <c r="D11" s="941" t="n"/>
       <c r="E11" s="948" t="inlineStr">
         <is>
-          <t>Destination Calculation read the actual demand inside Supplier System.</t>
+          <t>Calculation read the actual demand inside NSP.</t>
         </is>
       </c>
       <c r="F11" s="941" t="n"/>
@@ -13054,7 +13054,7 @@
       <c r="D12" s="941" t="n"/>
       <c r="E12" s="948" t="inlineStr">
         <is>
-          <t>The Supplier System table is fully replaced every run (delete - insert). In case any error</t>
+          <t>The NSP table is fully replaced every run (delete - insert). In case any error occurs, the run is</t>
         </is>
       </c>
       <c r="F12" s="941" t="n"/>
@@ -13167,7 +13167,7 @@
       <c r="D13" s="941" t="n"/>
       <c r="E13" s="948" t="inlineStr">
         <is>
-          <t>occurs, the run is rolled back and Supplier System keeps the data of the last successful run.</t>
+          <t>rolled back and NSP keeps the data of the last successful run.</t>
         </is>
       </c>
       <c r="F13" s="941" t="n"/>
@@ -13911,7 +13911,7 @@
       <c r="BD19" s="959" t="n"/>
       <c r="BE19" s="960" t="inlineStr">
         <is>
-          <t>(Supplier System)</t>
+          <t>(NSP)</t>
         </is>
       </c>
       <c r="BF19" s="961" t="n"/>
@@ -18986,7 +18986,7 @@
       <c r="CF18" s="999" t="n"/>
       <c r="CG18" s="1001" t="inlineStr">
         <is>
-          <t>SUMMARY (Supplier System).</t>
+          <t>SUMMARY (NSP).</t>
         </is>
       </c>
       <c r="CH18" s="999" t="n"/>
@@ -20407,7 +20407,7 @@
       <c r="CF31" s="999" t="n"/>
       <c r="CG31" s="1001" t="inlineStr">
         <is>
-          <t>leaves the Supplier System table</t>
+          <t>leaves the NSP table empty or</t>
         </is>
       </c>
       <c r="CH31" s="999" t="n"/>
@@ -20516,7 +20516,7 @@
       <c r="CF32" s="999" t="n"/>
       <c r="CG32" s="1001" t="inlineStr">
         <is>
-          <t>empty or half filled.</t>
+          <t>half filled.</t>
         </is>
       </c>
       <c r="CH32" s="999" t="n"/>
@@ -23123,7 +23123,7 @@
       <c r="J8" s="821" t="n"/>
       <c r="K8" s="1013" t="inlineStr">
         <is>
-          <t>TB_R_ACTUAL_DEMAND_SUMMARY (Supplier System)</t>
+          <t>TB_R_ACTUAL_DEMAND_SUMMARY (NSP)</t>
         </is>
       </c>
       <c r="L8" s="823" t="n"/>
@@ -23170,7 +23170,7 @@
       <c r="AW8" s="828" t="n"/>
       <c r="AX8" s="1014" t="inlineStr">
         <is>
-          <t>TB_R_ACTUAL_DEMAND_SUMMARY (Supplier System)</t>
+          <t>TB_R_ACTUAL_DEMAND_SUMMARY (NSP)</t>
         </is>
       </c>
       <c r="AY8" s="823" t="n"/>
@@ -27689,7 +27689,7 @@
       <c r="AW49" s="828" t="n"/>
       <c r="AX49" s="1014" t="inlineStr">
         <is>
-          <t>TB_R_ACTUAL_DEMAND_SUMMARY (Supplier System)</t>
+          <t>TB_R_ACTUAL_DEMAND_SUMMARY (NSP)</t>
         </is>
       </c>
       <c r="AY49" s="823" t="n"/>
@@ -33614,7 +33614,7 @@
       <c r="B8" s="942" t="n"/>
       <c r="C8" s="948" t="inlineStr">
         <is>
-          <t>This batch copies the actual demand summary from DB Surrounding into Supplier System once a</t>
+          <t>This batch copies the actual demand summary from DB Surrounding into NSP once a month.</t>
         </is>
       </c>
       <c r="D8" s="941" t="n"/>
@@ -33727,7 +33727,7 @@
       <c r="B9" s="942" t="n"/>
       <c r="C9" s="948" t="inlineStr">
         <is>
-          <t>month. Range of months and schedule are set in the system master (not explained in this</t>
+          <t>Range of months and schedule are set in the system master (not explained in this document).</t>
         </is>
       </c>
       <c r="D9" s="941" t="n"/>
@@ -33844,10 +33844,14 @@
       <c r="B10" s="942" t="n"/>
       <c r="C10" s="948" t="inlineStr">
         <is>
-          <t>document).</t>
-        </is>
-      </c>
-      <c r="D10" s="941" t="n"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D10" s="948" t="inlineStr">
+        <is>
+          <t>Full replace: all rows of the NSP table are deleted and all source rows are inserted (delete -</t>
+        </is>
+      </c>
       <c r="E10" s="941" t="n"/>
       <c r="F10" s="941" t="n"/>
       <c r="G10" s="941" t="n"/>
@@ -33959,14 +33963,10 @@
     <row r="11" ht="11.1" customHeight="1" s="710">
       <c r="A11" s="941" t="n"/>
       <c r="B11" s="942" t="n"/>
-      <c r="C11" s="948" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C11" s="941" t="n"/>
       <c r="D11" s="948" t="inlineStr">
         <is>
-          <t>Full replace: all rows of the Supplier System table are deleted and all source rows are inserted</t>
+          <t>insert). No row is compared or merged.</t>
         </is>
       </c>
       <c r="E11" s="941" t="n"/>
@@ -34080,10 +34080,14 @@
     <row r="12" ht="11.1" customHeight="1" s="710">
       <c r="A12" s="941" t="n"/>
       <c r="B12" s="942" t="n"/>
-      <c r="C12" s="941" t="n"/>
+      <c r="C12" s="948" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D12" s="948" t="inlineStr">
         <is>
-          <t>(delete - insert). No row is compared or merged.</t>
+          <t>All columns are copied with the same names and values; no conversion is done.</t>
         </is>
       </c>
       <c r="E12" s="941" t="n"/>
@@ -34204,7 +34208,7 @@
       </c>
       <c r="D13" s="948" t="inlineStr">
         <is>
-          <t>All columns are copied with the same names and values; no conversion is done.</t>
+          <t>Delete and insert run in one transaction (all-or-nothing). When the run fails, NSP keeps the data</t>
         </is>
       </c>
       <c r="E13" s="941" t="n"/>
@@ -34318,14 +34322,10 @@
     <row r="14" ht="11.1" customHeight="1" s="710">
       <c r="A14" s="941" t="n"/>
       <c r="B14" s="942" t="n"/>
-      <c r="C14" s="948" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C14" s="941" t="n"/>
       <c r="D14" s="948" t="inlineStr">
         <is>
-          <t>Delete and insert run in one transaction (all-or-nothing). When the run fails, Supplier System</t>
+          <t>of the last successful run.</t>
         </is>
       </c>
       <c r="E14" s="941" t="n"/>
@@ -34439,10 +34439,14 @@
     <row r="15" ht="11.1" customHeight="1" s="710">
       <c r="A15" s="941" t="n"/>
       <c r="B15" s="942" t="n"/>
-      <c r="C15" s="941" t="n"/>
+      <c r="C15" s="948" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D15" s="948" t="inlineStr">
         <is>
-          <t>keeps the data of the last successful run.</t>
+          <t>The batch must finish before the DAD Volume Calculation starts.</t>
         </is>
       </c>
       <c r="E15" s="941" t="n"/>
@@ -34556,16 +34560,8 @@
     <row r="16" ht="11.1" customHeight="1" s="710">
       <c r="A16" s="941" t="n"/>
       <c r="B16" s="942" t="n"/>
-      <c r="C16" s="948" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D16" s="948" t="inlineStr">
-        <is>
-          <t>The batch must finish before the DAD Volume Calculation starts.</t>
-        </is>
-      </c>
+      <c r="C16" s="941" t="n"/>
+      <c r="D16" s="941" t="n"/>
       <c r="E16" s="941" t="n"/>
       <c r="F16" s="941" t="n"/>
       <c r="G16" s="941" t="n"/>
@@ -39643,7 +39639,7 @@
       <c r="S16" s="955" t="n"/>
       <c r="T16" s="1031" t="inlineStr">
         <is>
-          <t>Insert into the Supplier System</t>
+          <t>Insert into the NSP table fails</t>
         </is>
       </c>
       <c r="U16" s="957" t="n"/>
@@ -39764,11 +39760,7 @@
       <c r="Q17" s="961" t="n"/>
       <c r="R17" s="961" t="n"/>
       <c r="S17" s="959" t="n"/>
-      <c r="T17" s="1039" t="inlineStr">
-        <is>
-          <t>table fails</t>
-        </is>
-      </c>
+      <c r="T17" s="1038" t="n"/>
       <c r="U17" s="961" t="n"/>
       <c r="V17" s="961" t="n"/>
       <c r="W17" s="961" t="n"/>
@@ -39800,7 +39792,7 @@
       <c r="AW17" s="959" t="n"/>
       <c r="AX17" s="1041" t="inlineStr">
         <is>
-          <t>TB_R_ACTUAL_DEMAND_SUMMARY into</t>
+          <t>TB_R_ACTUAL_DEMAND_SUMMARY into NSP:</t>
         </is>
       </c>
       <c r="AY17" s="961" t="n"/>
@@ -39911,7 +39903,7 @@
       <c r="AW18" s="965" t="n"/>
       <c r="AX18" s="1036" t="inlineStr">
         <is>
-          <t>Supplier System: &lt;ERROR_DETAIL&gt;.</t>
+          <t>&lt;ERROR_DETAIL&gt;.</t>
         </is>
       </c>
       <c r="AY18" s="967" t="n"/>
@@ -44247,7 +44239,7 @@
       <c r="D13" s="941" t="n"/>
       <c r="E13" s="948" t="inlineStr">
         <is>
-          <t>Transaction table - Actual demand summary replicated from DB Surrounding to Supplier System (same columns). Key (PK) proposed from the data; types follow the source table.</t>
+          <t>Transaction table - Actual demand summary replicated from DB Surrounding to NSP (same columns). Key (PK) proposed from the data; types follow the source table.</t>
         </is>
       </c>
       <c r="F13" s="941" t="n"/>
@@ -48542,7 +48534,7 @@
     <row r="1">
       <c r="A1" s="1044" t="inlineStr">
         <is>
-          <t>Sample data - Actual Demand Summary Sync to Supplier System</t>
+          <t>Sample data - Actual Demand Summary Sync to NSP</t>
         </is>
       </c>
     </row>
@@ -48556,7 +48548,7 @@
     <row r="3">
       <c r="A3" s="1045" t="inlineStr">
         <is>
-          <t>The batch copies every row of the source table; the Supplier System table is emptied first (delete - insert).</t>
+          <t>The batch copies every row of the source table; the NSP table is emptied first (delete - insert).</t>
         </is>
       </c>
     </row>
@@ -48851,7 +48843,7 @@
       </c>
       <c r="C16" s="1048" t="inlineStr">
         <is>
-          <t>Supplier System table emptied, 349,225 rows inserted. Log STATUS = SUCCESS.</t>
+          <t>NSP table emptied, 349,225 rows inserted. Log STATUS = SUCCESS.</t>
         </is>
       </c>
     </row>
@@ -48868,7 +48860,7 @@
       </c>
       <c r="C17" s="1048" t="inlineStr">
         <is>
-          <t>The row no longer exists in Supplier System (full replace).</t>
+          <t>The row no longer exists in NSP (full replace).</t>
         </is>
       </c>
     </row>
@@ -48885,7 +48877,7 @@
       </c>
       <c r="C18" s="1048" t="inlineStr">
         <is>
-          <t>Rolled back: Supplier System keeps the data of the last successful run. Log STATUS = FAILED.</t>
+          <t>Rolled back: NSP keeps the data of the last successful run. Log STATUS = FAILED.</t>
         </is>
       </c>
     </row>
